--- a/tests/fixtures/browser/spike/bounds-wide.xlsx
+++ b/tests/fixtures/browser/spike/bounds-wide.xlsx
@@ -72,7 +72,7 @@
           <t xml:space="preserve">可用功率</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="XFD1" t="inlineStr">
         <is>
           <t xml:space="preserve">末列</t>
         </is>
@@ -87,7 +87,7 @@
       <c r="B2">
         <v>29.6</v>
       </c>
-      <c r="C2">
+      <c r="XFD2">
         <v>1.5</v>
       </c>
     </row>
